--- a/Piaui/2026/Julho/ResultadosTRI_2EM_MT/Simulado_III/ResumoThetaIC_2EM_MT_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_2EM_MT/Simulado_III/ResumoThetaIC_2EM_MT_S3.xlsx
@@ -395,22 +395,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>308.655</v>
+        <v>309.444</v>
       </c>
       <c r="C2" t="n">
-        <v>307.604</v>
+        <v>308.397</v>
       </c>
       <c r="D2" t="n">
-        <v>309.707</v>
+        <v>310.49</v>
       </c>
       <c r="E2" t="n">
-        <v>61.531</v>
+        <v>61.083</v>
       </c>
       <c r="F2" t="n">
-        <v>59.992</v>
+        <v>59.554</v>
       </c>
       <c r="G2" t="n">
-        <v>63.07</v>
+        <v>62.612</v>
       </c>
     </row>
     <row r="3">
@@ -418,22 +418,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>1.173</v>
+        <v>1.189</v>
       </c>
       <c r="C3" t="n">
-        <v>1.152</v>
+        <v>1.168</v>
       </c>
       <c r="D3" t="n">
-        <v>1.194</v>
+        <v>1.21</v>
       </c>
       <c r="E3" t="n">
-        <v>1.231</v>
+        <v>1.222</v>
       </c>
       <c r="F3" t="n">
-        <v>1.211</v>
+        <v>1.202</v>
       </c>
       <c r="G3" t="n">
-        <v>1.25</v>
+        <v>1.241</v>
       </c>
     </row>
   </sheetData>
